--- a/Dados_Ranking.xlsx
+++ b/Dados_Ranking.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d83f4f4956eaf9a/CBCa/SUPERVISÃO/Ranking 2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1465563E-BF4D-425D-8A3B-3C171452C842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBD03FE4-2E86-40B5-9F43-8975EBE553F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="K1_Masc_Senior" sheetId="1" r:id="rId1"/>
@@ -18,31 +18,16 @@
     <sheet name="K1_Masc_Junior" sheetId="3" r:id="rId3"/>
     <sheet name="K1_Fem_Junior" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>Atleta</t>
   </si>
   <si>
-    <t>Murillo Sorgetz</t>
-  </si>
-  <si>
-    <t>Emanoel Souza</t>
-  </si>
-  <si>
-    <t>Allan Ferreira</t>
-  </si>
-  <si>
-    <t>Pedro Aversa</t>
-  </si>
-  <si>
-    <t>Fabio Scchena</t>
-  </si>
-  <si>
     <t>Copa_Individual</t>
   </si>
   <si>
@@ -53,6 +38,120 @@
   </si>
   <si>
     <t>Brasileiro_Cross</t>
+  </si>
+  <si>
+    <t>KAUA LUIZ AMARAL DA SILVA</t>
+  </si>
+  <si>
+    <t>MURILLO SORGETZ</t>
+  </si>
+  <si>
+    <t>EMANOEL SOUZA</t>
+  </si>
+  <si>
+    <t>ALLAN FERREIRA</t>
+  </si>
+  <si>
+    <t>FABIO SCCHENA</t>
+  </si>
+  <si>
+    <t>PEDRO GONCALVES</t>
+  </si>
+  <si>
+    <t>GUILHERME MAPELLI</t>
+  </si>
+  <si>
+    <t>JOSE AUGUSTO DE SOUZA</t>
+  </si>
+  <si>
+    <t>ANDRE LUIZ DE PAULA</t>
+  </si>
+  <si>
+    <t>PATRICIO LEO DI MONACO</t>
+  </si>
+  <si>
+    <t>GABRIEL ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>DAVI SANTHIAGO RIBEIRO</t>
+  </si>
+  <si>
+    <t>GERSON TERRES JUNIOR</t>
+  </si>
+  <si>
+    <t>NILSON DOS SANTOS RODRIGUES</t>
+  </si>
+  <si>
+    <t>JOAO VICTOR DE FREITAS</t>
+  </si>
+  <si>
+    <t>PEDRO BALEM FROIS</t>
+  </si>
+  <si>
+    <t>KAUE DA SILVA FERREIRA</t>
+  </si>
+  <si>
+    <t>NICOLLAS COSTA PEDROSO</t>
+  </si>
+  <si>
+    <t>GABRIEL BALEM FROIS</t>
+  </si>
+  <si>
+    <t>MAX CUNHA RODRIGUES</t>
+  </si>
+  <si>
+    <t>LUAN GABRIEL COLVERO</t>
+  </si>
+  <si>
+    <t>THOMAS DE OLIVEIRA NERES</t>
+  </si>
+  <si>
+    <t>KEVYN GABRIEL BELICA CARNEIRO</t>
+  </si>
+  <si>
+    <t>LUIS OTAVIO DOS SANTOS FONSECA</t>
+  </si>
+  <si>
+    <t>JOAO GABRIEL DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>KAUAN HENRIQUE RAMOS</t>
+  </si>
+  <si>
+    <t>GUILHERME CAMUZZI GRANDIS</t>
+  </si>
+  <si>
+    <t>JOAO PEDRO MENDONCA</t>
+  </si>
+  <si>
+    <t>JHONAS COSTA PEDROSO</t>
+  </si>
+  <si>
+    <t>SALVADOR VALENZUELA CORTES</t>
+  </si>
+  <si>
+    <t>OTAVIO RAFAEL OLIVEIRA FANHA</t>
+  </si>
+  <si>
+    <t>ANTONIO FERREIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>ANDERSON SILVA DA CRUZ</t>
+  </si>
+  <si>
+    <t>VINICIUS COSTA DE PAULA</t>
+  </si>
+  <si>
+    <t>RAY EDUARDO DA COSTA</t>
+  </si>
+  <si>
+    <t>MATHEUS HENRIQUE TAY ROSA</t>
+  </si>
+  <si>
+    <t>VICTOR GABRIEL DOS SANTOS PEREIRA</t>
+  </si>
+  <si>
+    <t>ROGER HENRIQUE DA COSTA</t>
   </si>
 </sst>
 </file>
@@ -429,29 +528,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -468,7 +574,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -477,15 +583,15 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -494,15 +600,15 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -511,15 +617,15 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -528,16 +634,82 @@
         <v>5</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="E6">
-        <v>6</v>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10">
+        <v>7</v>
+      </c>
+      <c r="E10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>8</v>
+      </c>
+      <c r="E11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:E6 A1" numberStoredAsText="1"/>
+    <ignoredError sqref="B2:E2 A1 B6:C6 B5:C5 B4:C4 B3:C3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -546,6 +718,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F3C43FF-ECDE-4AA1-8EA0-365A2BCD9639}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -553,9 +733,493 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C4383A5-CA5E-4F90-BD86-4C26B95DF6E6}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="31.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5">
+        <v>19</v>
+      </c>
+      <c r="C5">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <v>11</v>
+      </c>
+      <c r="C11">
+        <v>8</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>13</v>
+      </c>
+      <c r="D12">
+        <v>11</v>
+      </c>
+      <c r="E12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
+      <c r="E13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>13</v>
+      </c>
+      <c r="E14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>20</v>
+      </c>
+      <c r="D15">
+        <v>14</v>
+      </c>
+      <c r="E15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16">
+        <v>15</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>12</v>
+      </c>
+      <c r="D17">
+        <v>16</v>
+      </c>
+      <c r="E17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>17</v>
+      </c>
+      <c r="E18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>18</v>
+      </c>
+      <c r="E19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20">
+        <v>17</v>
+      </c>
+      <c r="C20">
+        <v>17</v>
+      </c>
+      <c r="D20">
+        <v>19</v>
+      </c>
+      <c r="E20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>20</v>
+      </c>
+      <c r="E21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>21</v>
+      </c>
+      <c r="E22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23">
+        <v>8</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>22</v>
+      </c>
+      <c r="E23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>23</v>
+      </c>
+      <c r="E24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25">
+        <v>10</v>
+      </c>
+      <c r="C25">
+        <v>5</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26">
+        <v>13</v>
+      </c>
+      <c r="C26">
+        <v>6</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27">
+        <v>15</v>
+      </c>
+      <c r="C27">
+        <v>15</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28">
+        <v>16</v>
+      </c>
+      <c r="C28">
+        <v>16</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/Dados_Ranking.xlsx
+++ b/Dados_Ranking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d83f4f4956eaf9a/CBCa/SUPERVISÃO/Ranking 2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBD03FE4-2E86-40B5-9F43-8975EBE553F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{EBD03FE4-2E86-40B5-9F43-8975EBE553F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5D52AF8-88CF-45AE-A358-AF3E96E55F36}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="K1_Masc_Senior" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="62">
   <si>
     <t>Atleta</t>
   </si>
@@ -43,36 +43,15 @@
     <t>KAUA LUIZ AMARAL DA SILVA</t>
   </si>
   <si>
-    <t>MURILLO SORGETZ</t>
-  </si>
-  <si>
-    <t>EMANOEL SOUZA</t>
-  </si>
-  <si>
-    <t>ALLAN FERREIRA</t>
-  </si>
-  <si>
-    <t>FABIO SCCHENA</t>
-  </si>
-  <si>
-    <t>PEDRO GONCALVES</t>
-  </si>
-  <si>
     <t>GUILHERME MAPELLI</t>
   </si>
   <si>
-    <t>JOSE AUGUSTO DE SOUZA</t>
-  </si>
-  <si>
     <t>ANDRE LUIZ DE PAULA</t>
   </si>
   <si>
     <t>PATRICIO LEO DI MONACO</t>
   </si>
   <si>
-    <t>GABRIEL ALBUQUERQUE</t>
-  </si>
-  <si>
     <t>DAVI SANTHIAGO RIBEIRO</t>
   </si>
   <si>
@@ -152,6 +131,84 @@
   </si>
   <si>
     <t>ROGER HENRIQUE DA COSTA</t>
+  </si>
+  <si>
+    <t>MURILLO GUILHERME DA SILVA SORGETZ</t>
+  </si>
+  <si>
+    <t>ALLAN KAUA DA SILVA FERREIRA</t>
+  </si>
+  <si>
+    <t>JOSE AUGUSTO VIEIRA DE SOUZA</t>
+  </si>
+  <si>
+    <t>KLEBER DOS SANTOS KERLING</t>
+  </si>
+  <si>
+    <t>PEDRO HENRIQUE AVANSI AVERSA</t>
+  </si>
+  <si>
+    <t>EMANOEL BARCELOS CRUZ DE SOUZA</t>
+  </si>
+  <si>
+    <t>GABRIEL DE ALBUQUERQUE SILVA</t>
+  </si>
+  <si>
+    <t>DIOGO MANOMICS DIAS</t>
+  </si>
+  <si>
+    <t>NATAN DA SILVA FROS</t>
+  </si>
+  <si>
+    <t>HENRIQUE AUGUSTO LOURENCO DE SOUZA</t>
+  </si>
+  <si>
+    <t>BEATRIZ DE PAULA SIMOES DA MOTTA</t>
+  </si>
+  <si>
+    <t>BRUNA DA SILVA SIQUEIRA</t>
+  </si>
+  <si>
+    <t>MARIA ERNESTINA DA MATTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIELA SOFIA </t>
+  </si>
+  <si>
+    <t>MICAELLY HENRIQUE DE GODOI</t>
+  </si>
+  <si>
+    <t>ANNA CLARA LEAL DE MORAES</t>
+  </si>
+  <si>
+    <t>IASMIN TANI</t>
+  </si>
+  <si>
+    <t>IZABELLY GALVAO DE FREITAS</t>
+  </si>
+  <si>
+    <t>EMILLY SHARA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>OLINDA DO CARMO MALDONADO GONCALVES</t>
+  </si>
+  <si>
+    <t>MONIQUE JEANNE DE PAULA VIEIRA</t>
+  </si>
+  <si>
+    <t>NICOLE ROCHA GOMIDES</t>
+  </si>
+  <si>
+    <t>EMANUELY MAIARA RODRIGUES BIRKHEUER</t>
+  </si>
+  <si>
+    <t>MILENA SOFIA</t>
+  </si>
+  <si>
+    <t>PEDRO HENRIQUE GONCALVES</t>
+  </si>
+  <si>
+    <t>OMIRA ESTACIA NETA</t>
   </si>
 </sst>
 </file>
@@ -528,10 +585,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.75" bestFit="1" customWidth="1"/>
@@ -557,7 +614,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -574,24 +631,24 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -608,30 +665,30 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -642,91 +699,298 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>40</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>41</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>42</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
       </c>
       <c r="D10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E10">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>43</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
         <v>15</v>
       </c>
-      <c r="D12">
-        <v>10</v>
-      </c>
       <c r="E12">
-        <v>10</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="B2:E2 A1 B6:C6 B5:C5 B4:C4 B3:C3" numberStoredAsText="1"/>
+    <ignoredError sqref="B2 A1 B6 B5 B4 B3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F3C43FF-ECDE-4AA1-8EA0-365A2BCD9639}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="31.25" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -762,7 +1026,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -779,7 +1043,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -796,7 +1060,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>18</v>
@@ -813,7 +1077,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B5">
         <v>19</v>
@@ -830,7 +1094,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <v>9</v>
@@ -847,7 +1111,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -864,7 +1128,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -881,7 +1145,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>3</v>
@@ -898,7 +1162,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -915,7 +1179,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>11</v>
@@ -932,7 +1196,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B12">
         <v>6</v>
@@ -949,7 +1213,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -966,7 +1230,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -983,7 +1247,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <v>20</v>
@@ -1000,7 +1264,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>4</v>
@@ -1017,7 +1281,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B17">
         <v>14</v>
@@ -1034,7 +1298,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1051,7 +1315,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1068,7 +1332,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>17</v>
@@ -1085,7 +1349,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1102,7 +1366,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1119,7 +1383,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B23">
         <v>8</v>
@@ -1136,7 +1400,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1153,7 +1417,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B25">
         <v>10</v>
@@ -1170,7 +1434,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B26">
         <v>13</v>
@@ -1187,7 +1451,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B27">
         <v>15</v>
@@ -1204,7 +1468,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B28">
         <v>16</v>
@@ -1226,9 +1490,202 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2C17466-B722-43E1-AD21-68B030763224}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="40.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>7</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>